--- a/templates/02_financeiro/06_controle_contas_pagar_receber.xlsx
+++ b/templates/02_financeiro/06_controle_contas_pagar_receber.xlsx
@@ -4,22 +4,125 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Controle_Contas_Pagar_Receber" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Contas a Receber" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Contas a Pagar" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
   <si>
     <t>Data</t>
   </si>
   <si>
+    <t>Cliente</t>
+  </si>
+  <si>
     <t>Descrição</t>
   </si>
   <si>
-    <t>Valor</t>
+    <t>Valor (R$)</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>01/01/2026</t>
+  </si>
+  <si>
+    <t>Cliente A</t>
+  </si>
+  <si>
+    <t>Projeto Web</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>10/01/2026</t>
+  </si>
+  <si>
+    <t>Pago</t>
+  </si>
+  <si>
+    <t>05/01/2026</t>
+  </si>
+  <si>
+    <t>Cliente B</t>
+  </si>
+  <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>15/01/2026</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Cliente C</t>
+  </si>
+  <si>
+    <t>Branding</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>20/01/2026</t>
+  </si>
+  <si>
+    <t>**TOTAL**</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>**[SUM: D]**</t>
+  </si>
+  <si>
+    <t>Fornecedor</t>
+  </si>
+  <si>
+    <t>02/01/2026</t>
+  </si>
+  <si>
+    <t>Imobiliária</t>
+  </si>
+  <si>
+    <t>Aluguel</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>Mensalidade</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>12/01/2026</t>
+  </si>
+  <si>
+    <t>AWS</t>
+  </si>
+  <si>
+    <t>Servidores</t>
+  </si>
+  <si>
+    <t>300</t>
   </si>
 </sst>
 </file>
@@ -37,7 +140,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,9 +169,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,10 +509,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="6" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -421,6 +524,209 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="6" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
